--- a/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.21%2510</t>
+          <t>-0.4%2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.21%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2510</v>
+        <v>2500</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.35%753,000</t>
+          <t>9.42%753,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.35%</t>
+          <t>9.42%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+1.22%4980</t>
+          <t>-0.6%4950</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+1.22%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>4980</v>
+        <v>4950</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.13%249,000</t>
+          <t>6.18%249,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.13%</t>
+          <t>6.18%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.82%11835</t>
+          <t>+2.62%12145</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>+2.62%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>11835</v>
+        <v>12145</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4.04%67,000</t>
+          <t>3.95%67,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.04%</t>
+          <t>3.95%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,25 +692,25 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+0.81%4975</t>
+          <t>+4.22%5185</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+4.22%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>4975</v>
+        <v>5185</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.85%156,000</t>
+          <t>3.87%156,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.85%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.16%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.79%1905</t>
+          <t>-1.05%1885</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.79%</t>
+          <t>-1.05%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>1905</v>
+        <v>1885</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.82%404,000</t>
+          <t>3.83%404,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.82%</t>
+          <t>3.83%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.4%1215</t>
+          <t>+7.41%1305</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.4%</t>
+          <t>+7.41%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>1215</v>
+        <v>1305</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.68%625,000</t>
+          <t>3.78%625,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.68%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.26%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+1.1%6875</t>
+          <t>-1.09%6800</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+1.1%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6875</v>
+        <v>6800</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.10%91,000</t>
+          <t>3.12%91,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.12%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.59%254</t>
+          <t>+2.36%260</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.59%</t>
+          <t>+2.36%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.09%2,416,000</t>
+          <t>3.06%2,416,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.06%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0%519</t>
+          <t>+1.35%526</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.35%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.85%1,096,000</t>
+          <t>2.83%1,096,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.27%5490</t>
+          <t>+1.64%5580</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.27%</t>
+          <t>+1.64%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>5490</v>
+        <v>5580</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.51%91,000</t>
+          <t>2.49%91,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.49%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.74%7900</t>
+          <t>-1.99%3440</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.74%</t>
+          <t>-1.99%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7900</v>
+        <v>3440</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.38%59,000</t>
+          <t>2.34%134,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>59000</v>
+        <v>134000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.18%3510</t>
+          <t>0%7900</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3510</v>
+        <v>7900</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.30%134,000</t>
+          <t>2.32%59,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.32%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>134000</v>
+        <v>59000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,25 +1236,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.23%1095</t>
+          <t>+0.42%713</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.23%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1095</v>
+        <v>713</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.20%393,000</t>
+          <t>2.20%621,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1263,11 +1263,11 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>393000</v>
+        <v>621000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+1%710</t>
+          <t>-1.3%2660</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>710</v>
+        <v>2660</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.19%621,000</t>
+          <t>2.14%161,600</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.19%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>621000</v>
+        <v>161600</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:41</t>
+          <t>2026-10-02 19:05:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-1.3%2660</t>
+          <t>+0.91%1105</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>+0.91%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>2660</v>
+        <v>1105</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.18%161,600</t>
+          <t>2.14%393,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.14%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>161600</v>
+        <v>393000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+0.28%180</t>
+          <t>-0.56%179</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+0.28%</t>
+          <t>-0.56%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+0.99%254</t>
+          <t>-1.18%251</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2.04%1,616,000</t>
+          <t>2.05%1,616,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2.04%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1559,12 +1559,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.91%20,300</t>
+          <t>1.93%20,300</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.90%74,000</t>
+          <t>1.85%74,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.85%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.7%5770</t>
+          <t>+2.82%1460</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>+2.82%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5770</v>
+        <v>1460</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.81%61,000</t>
+          <t>1.78%251,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>61000</v>
+        <v>251000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.81%168,000</t>
+          <t>1.77%168,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.97%1420</t>
+          <t>+5.2%6070</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.97%</t>
+          <t>+5.2%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1420</v>
+        <v>6070</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.68%251,000</t>
+          <t>1.75%61,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>251000</v>
+        <v>61000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.96%2110</t>
+          <t>+3.42%1965</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>+3.42%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2110</v>
+        <v>1965</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.62%155,105</t>
+          <t>1.65%174,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>155105</v>
+        <v>174000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.58%2080</t>
+          <t>-1.18%2085</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>-1.18%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2080</v>
+        <v>2085</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.58%148,000</t>
+          <t>1.63%155,105</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>148000</v>
+        <v>155105</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+7.04%1900</t>
+          <t>+5.29%2190</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+7.04%</t>
+          <t>+5.29%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1900</v>
+        <v>2190</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.55%174,000</t>
+          <t>1.53%148,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>174000</v>
+        <v>148000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+0.99%1535</t>
+          <t>+3.99%626</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+0.99%</t>
+          <t>+3.99%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1535</v>
+        <v>626</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.37%180,000</t>
+          <t>1.45%485,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>180000</v>
+        <v>485000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+9.85%602</t>
+          <t>+0.99%1535</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+0.99%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>602</v>
+        <v>1535</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.33%485,000</t>
+          <t>1.38%180,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>485000</v>
+        <v>180000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+4.12%1010</t>
+          <t>+3.96%1050</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+4.12%</t>
+          <t>+3.96%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1010</v>
+        <v>1050</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.29%266,000</t>
+          <t>1.34%266,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.34%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,25 +2217,25 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.25%190.5</t>
+          <t>-2.1%186.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>190.5</v>
+        <v>186.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20%1,298,000</t>
+          <t>1.23%1,298,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.23%</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:42</t>
+          <t>2026-10-02 19:05:18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2382廣達</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.15%334</t>
+          <t>-2%835</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-2%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>334</v>
+        <v>835</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.20%718,000</t>
+          <t>1.21%286,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>718000</v>
+        <v>286000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+3.41%212.5</t>
+          <t>+0.47%213.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+3.41%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>212.5</v>
+        <v>213.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.18%1,147,000</t>
+          <t>1.21%1,147,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>2382廣達</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+7.71%852</t>
+          <t>-0.6%332</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+7.71%</t>
+          <t>-0.6%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>852</v>
+        <v>332</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.13%286,000</t>
+          <t>1.19%718,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>286000</v>
+        <v>718000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+3.05%642</t>
+          <t>+6.39%683</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+3.05%</t>
+          <t>+6.39%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>642</v>
+        <v>683</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.03%330,000</t>
+          <t>1.06%330,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.03%</t>
+          <t>1.06%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.99%252,000</t>
+          <t>1.02%252,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.73%67.9</t>
+          <t>-0.88%67.3</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.73%</t>
+          <t>-0.88%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>67.90000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.95%2,781,000</t>
+          <t>0.94%2,781,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+1.11%45.35</t>
+          <t>0%45.35</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+1.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.90%4,029,622</t>
+          <t>0.91%4,029,622</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.79%368.5</t>
+          <t>+1.36%373.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.79%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>368.5</v>
+        <v>373.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.87%484,000</t>
+          <t>0.89%484,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.89%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3264欣銓</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.82%245.5</t>
+          <t>+1.37%6290</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.82%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>245.5</v>
+        <v>6290</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.79%650,000</t>
+          <t>0.80%26,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>650000</v>
+        <v>26000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>5904寶雅*</t>
+          <t>3264欣銓</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-0.86%69.1</t>
+          <t>+0.82%245.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-0.86%</t>
+          <t>+0.82%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>69.09999999999999</v>
+        <v>245.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.79%2,255,500</t>
+          <t>0.80%650,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>2255500</v>
+        <v>650000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>5904寶雅*</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+4.37%6205</t>
+          <t>-0.86%69.1</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+4.37%</t>
+          <t>-0.86%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>6205</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.77%26,000</t>
+          <t>0.78%2,255,500</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.78%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>26000</v>
+        <v>2255500</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-2.49%1565</t>
+          <t>0%161.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1565</v>
+        <v>161.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.77%96,000</t>
+          <t>0.75%929,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.77%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>96000</v>
+        <v>929000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.82%3245</t>
+          <t>-3.51%1510</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.82%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>3245</v>
+        <v>1510</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.73%44,000</t>
+          <t>0.75%96,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.75%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>44000</v>
+        <v>96000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.53%161.5</t>
+          <t>-1.82%3245</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.53%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>161.5</v>
+        <v>3245</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.72%929,000</t>
+          <t>0.71%44,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.71%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>929000</v>
+        <v>44000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-2.65%2390</t>
+          <t>-3.35%2310</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-2.65%</t>
+          <t>-3.35%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>2390</v>
+        <v>2310</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.66%54,000</t>
+          <t>0.64%54,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.66%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:44</t>
+          <t>2026-10-02 19:05:19</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.54%2555</t>
+          <t>-0.59%2540</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>-0.59%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>2555</v>
+        <v>2540</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.63%48,336</t>
+          <t>0.62%48,336</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.63%</t>
+          <t>0.62%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:45</t>
+          <t>2026-10-02 19:05:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+0.76%529</t>
+          <t>+2.46%542</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+0.76%</t>
+          <t>+2.46%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:45</t>
+          <t>2026-10-02 19:05:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:45</t>
+          <t>2026-10-02 19:05:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.64%474.5</t>
+          <t>+1.37%481</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.64%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>474.5</v>
+        <v>481</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:45</t>
+          <t>2026-10-02 19:05:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+1.08%845</t>
+          <t>-0.47%841</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-0.47%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 00:26:45</t>
+          <t>2026-10-02 19:05:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-0.67%1480</t>
+          <t>+9.8%1625</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-0.67%</t>
+          <t>+9.8%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1480</v>
+        <v>1625</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:16</t>
+          <t>2026-10-02 22:49:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:18</t>
+          <t>2026-10-02 22:49:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:19</t>
+          <t>2026-10-02 22:49:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:20</t>
+          <t>2026-10-02 22:49:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:20</t>
+          <t>2026-10-02 22:49:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:20</t>
+          <t>2026-10-02 22:49:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:20</t>
+          <t>2026-10-02 22:49:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 19:05:20</t>
+          <t>2026-10-02 22:49:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:42</t>
+          <t>2026-10-02 22:58:21</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:43</t>
+          <t>2026-10-02 22:58:22</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:44</t>
+          <t>2026-10-02 22:58:23</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:46</t>
+          <t>2026-10-02 22:58:25</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:46</t>
+          <t>2026-10-02 22:58:25</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:46</t>
+          <t>2026-10-02 22:58:25</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:46</t>
+          <t>2026-10-02 22:58:25</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:49:46</t>
+          <t>2026-10-02 22:58:25</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-02_00980A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:21</t>
+          <t>2026-10-02 23:48:08</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:22</t>
+          <t>2026-10-02 23:48:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:23</t>
+          <t>2026-10-02 23:48:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:25</t>
+          <t>2026-10-02 23:48:12</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:25</t>
+          <t>2026-10-02 23:48:12</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:25</t>
+          <t>2026-10-02 23:48:12</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:25</t>
+          <t>2026-10-02 23:48:12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-02 22:58:25</t>
+          <t>2026-10-02 23:48:12</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
